--- a/traffic_capt.xlsx
+++ b/traffic_capt.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NOC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B824EE20-9836-4E5B-AB3F-DCC12527AC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>site_id</t>
   </si>
@@ -30,12 +24,15 @@
   <si>
     <t>AM16224607741106N</t>
   </si>
+  <si>
+    <t>Done Capture</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,21 +95,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -150,7 +139,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -184,7 +173,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -219,10 +207,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +382,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -407,9 +394,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/traffic_capt.xlsx
+++ b/traffic_capt.xlsx
@@ -25,7 +25,36 @@
     <t>AM16224607741106N</t>
   </si>
   <si>
-    <t>Done Capture</t>
+    <t xml:space="preserve">Error saat proses site AM16224607741106N: Login gagal: Message: element click intercepted: Element &lt;button type="submit" class="mt-1 v-btn v-btn--block v-btn--disabled v-btn--has-bg theme--light v-size--default" disabled="disabled"&gt;...&lt;/button&gt; is not clickable at point (769, 518). Other element would receive the click: &lt;div class="py-3"&gt;...&lt;/div&gt;
+  (Session info: chrome=132.0.6834.83)
+Stacktrace:
+	GetHandleVerifier [0x008B74A3+25091]
+	(No symbol) [0x0083DC04]
+	(No symbol) [0x0071B373]
+	(No symbol) [0x007654B8]
+	(No symbol) [0x007638C4]
+	(No symbol) [0x00761467]
+	(No symbol) [0x0076076A]
+	(No symbol) [0x007553A5]
+	(No symbol) [0x00781F0C]
+	(No symbol) [0x00754E44]
+	(No symbol) [0x007821A4]
+	(No symbol) [0x0079B49E]
+	(No symbol) [0x00781CA6]
+	(No symbol) [0x007531D5]
+	(No symbol) [0x0075435D]
+	GetHandleVerifier [0x00BB07C3+3142947]
+	GetHandleVerifier [0x00BC1A2B+3213195]
+	GetHandleVerifier [0x00BBC412+3191154]
+	GetHandleVerifier [0x00958720+685184]
+	(No symbol) [0x00846E1D]
+	(No symbol) [0x00843E18]
+	(No symbol) [0x00843FB6]
+	(No symbol) [0x008366F0]
+	BaseThreadInitThunk [0x767C5D49+25]
+	RtlInitializeExceptionChain [0x7796CDEB+107]
+	RtlGetAppContainerNamedObjectPath [0x7796CD71+561]
+</t>
   </si>
 </sst>
 </file>

--- a/traffic_capt.xlsx
+++ b/traffic_capt.xlsx
@@ -25,36 +25,7 @@
     <t>AM16224607741106N</t>
   </si>
   <si>
-    <t xml:space="preserve">Error saat proses site AM16224607741106N: Login gagal: Message: element click intercepted: Element &lt;button type="submit" class="mt-1 v-btn v-btn--block v-btn--disabled v-btn--has-bg theme--light v-size--default" disabled="disabled"&gt;...&lt;/button&gt; is not clickable at point (769, 518). Other element would receive the click: &lt;div class="py-3"&gt;...&lt;/div&gt;
-  (Session info: chrome=132.0.6834.83)
-Stacktrace:
-	GetHandleVerifier [0x008B74A3+25091]
-	(No symbol) [0x0083DC04]
-	(No symbol) [0x0071B373]
-	(No symbol) [0x007654B8]
-	(No symbol) [0x007638C4]
-	(No symbol) [0x00761467]
-	(No symbol) [0x0076076A]
-	(No symbol) [0x007553A5]
-	(No symbol) [0x00781F0C]
-	(No symbol) [0x00754E44]
-	(No symbol) [0x007821A4]
-	(No symbol) [0x0079B49E]
-	(No symbol) [0x00781CA6]
-	(No symbol) [0x007531D5]
-	(No symbol) [0x0075435D]
-	GetHandleVerifier [0x00BB07C3+3142947]
-	GetHandleVerifier [0x00BC1A2B+3213195]
-	GetHandleVerifier [0x00BBC412+3191154]
-	GetHandleVerifier [0x00958720+685184]
-	(No symbol) [0x00846E1D]
-	(No symbol) [0x00843E18]
-	(No symbol) [0x00843FB6]
-	(No symbol) [0x008366F0]
-	BaseThreadInitThunk [0x767C5D49+25]
-	RtlInitializeExceptionChain [0x7796CDEB+107]
-	RtlGetAppContainerNamedObjectPath [0x7796CD71+561]
-</t>
+    <t>Done Capture</t>
   </si>
 </sst>
 </file>
